--- a/04_DESIGN_TABLES/DesignTable_2701_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2701_SW2.xlsx
@@ -837,13 +837,13 @@
         <v>0.375</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.43301</v>
+        <v>0.43251</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -1025,13 +1025,13 @@
         <v>0.219</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.12644</v>
+        <v>0.12594</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.12644</v>
+        <v>0.12594</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.25288</v>
+        <v>0.25238</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1218,13 +1218,13 @@
         <v>0.22</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1406,13 +1406,13 @@
         <v>0.281</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.16224</v>
+        <v>0.16174</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.16224</v>
+        <v>0.16174</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.32447</v>
+        <v>0.32397</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
@@ -1599,13 +1599,13 @@
         <v>0.28125</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.16238</v>
+        <v>0.16188</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.16238</v>
+        <v>0.16188</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.32476</v>
+        <v>0.32426</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
@@ -1792,13 +1792,13 @@
         <v>0.28125</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.16238</v>
+        <v>0.16188</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.16238</v>
+        <v>0.16188</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.32476</v>
+        <v>0.32426</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1985,13 +1985,13 @@
         <v>0.375</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.43301</v>
+        <v>0.43251</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
@@ -2173,13 +2173,13 @@
         <v>0.44</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.50807</v>
+        <v>0.50757</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
@@ -2361,13 +2361,13 @@
         <v>0.44</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.50807</v>
+        <v>0.50757</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
@@ -2549,13 +2549,13 @@
         <v>0.53125</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.30672</v>
+        <v>0.30622</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.30672</v>
+        <v>0.30622</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.61343</v>
+        <v>0.61293</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
@@ -2742,13 +2742,13 @@
         <v>0.53125</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.30672</v>
+        <v>0.30622</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.30672</v>
+        <v>0.30622</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.61343</v>
+        <v>0.61293</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
@@ -2935,13 +2935,13 @@
         <v>0.65625</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.37889</v>
+        <v>0.37839</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.37889</v>
+        <v>0.37839</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.7577700000000001</v>
+        <v>0.75727</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
@@ -3128,13 +3128,13 @@
         <v>0.65625</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.37889</v>
+        <v>0.37839</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.37889</v>
+        <v>0.37839</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.7577700000000001</v>
+        <v>0.75727</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
@@ -3321,13 +3321,13 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.94108</v>
+        <v>0.94058</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
@@ -3509,13 +3509,13 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.94108</v>
+        <v>0.94058</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>

--- a/04_DESIGN_TABLES/DesignTable_2701_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2701_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE16"/>
+  <dimension ref="A1:BE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1082,32 +1082,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2701-04-04-FG</t>
+          <t>2701-02-02-FG-LN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.97</v>
+        <v>0.88</v>
       </c>
       <c r="C4" t="n">
-        <v>0.22</v>
+        <v>0.219</v>
       </c>
       <c r="D4" t="n">
-        <v>0.21875</v>
+        <v>0.15625</v>
       </c>
       <c r="E4" t="n">
-        <v>0.075</v>
+        <v>0.063</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2608</v>
+        <v>0.19</v>
       </c>
       <c r="G4" t="n">
-        <v>0.182</v>
+        <v>0.125</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0795</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1135</v>
+        <v>0.1108</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
@@ -1116,34 +1116,34 @@
         <v>37</v>
       </c>
       <c r="L4" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2</v>
+        <v>0.199</v>
       </c>
       <c r="N4" t="n">
-        <v>0.28</v>
+        <v>0.219</v>
       </c>
       <c r="O4" t="n">
-        <v>0.09</v>
+        <v>0.094</v>
       </c>
       <c r="P4" t="n">
-        <v>0.21875</v>
+        <v>0.15625</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.075</v>
+        <v>0.063</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7308</v>
+        <v>0.662</v>
       </c>
       <c r="S4" t="n">
-        <v>0.182</v>
+        <v>0.125</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0795</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1135</v>
+        <v>0.1108</v>
       </c>
       <c r="V4" t="n">
         <v>60</v>
@@ -1152,88 +1152,88 @@
         <v>37</v>
       </c>
       <c r="X4" t="n">
-        <v>0.17</v>
+        <v>0.062</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.97</v>
+        <v>0.88</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.17</v>
+        <v>0.062</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4375</v>
+        <v>0.3125</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.05</v>
+        <v>0.04167</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.2608</v>
+        <v>0.19</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.02706</v>
+        <v>0.02255</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0125</v>
+        <v>0.01042</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.05</v>
+        <v>0.04167</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.4375</v>
+        <v>0.3125</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.05</v>
+        <v>0.04167</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.7308</v>
+        <v>0.662</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.02706</v>
+        <v>0.02255</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0125</v>
+        <v>0.01042</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.05</v>
+        <v>0.04167</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.44</v>
+        <v>0.438</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.42</v>
+        <v>0.432</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.44</v>
+        <v>0.438</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.48</v>
+        <v>0.486</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.22</v>
+        <v>0.219</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.22</v>
+        <v>0.219</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.12652</v>
+        <v>0.12594</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.12652</v>
+        <v>0.12594</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.25353</v>
+        <v>0.25238</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2701-04-04-FG</t>
+          <t>2701-02-02-FG-LN</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>90 deg Bulkhead Elbow, 7/16-20 JIC x 7/16-20 JIC bulkhead</t>
+          <t>90 deg Bulkhead Elbow, 5/16-24 JIC x 5/16-24 JIC bulkhead</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>7/16-20 JIC</t>
+          <t>5/16-24 JIC</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>7/16-20 JIC bulkhead</t>
+          <t>5/16-24 JIC bulkhead</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1258,38 +1258,43 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>Air-Way s123 only (double-pass 33 rows); pass1 stated ROWS=34, both passes enumerate 33; Series sheet n=34 -&gt; 33 accepted | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; bulkhead leg (Brennan 2701-08-08-FG STEP): hex arm -&gt; round collar of Air-Way dia O (flush with the hex flats where Air-Way prints O = the flats, e.g. 2701 -06/-10/-12; the revolved core under the hex arm is drawn 0.02 inside the flats and is hidden by the hex) -&gt; JIC bulkhead end, relief to tip = Air-Way i2 (STEP 2.11 - 0.86 = 1.25 = i2), JIC thread run from the relief to the land; K1 read as the collar thickness (ASSUMPTION: the STEP collar is 0.875 x 0.125 followed by a 0.125 round shank at the thread dia, not modelled); -LN configs ship with a locknut (separate part, not modelled); each leg bore runs from its face to the axis crossing</t>
+          <t>OMi catalog SKU 2701-LN-02-02-FG dropped by the 2026-09-23 crawl (adapters77 2026-10-16); -LN = the plain 2701-02-02-FG + a locknut (A10 Q-TRANSFER-LN yes 2026-10-18): every size = row 2701-02-02-FG (its own Brennan STEP, batch 15) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; bulkhead leg (Brennan 2701-08-08-FG STEP): hex arm -&gt; round collar of Air-Way dia O (flush with the hex flats where Air-Way prints O = the flats, e.g. 2701 -06/-10/-12; the revolved core under the hex arm is drawn 0.02 inside the flats and is hidden by the hex) -&gt; JIC bulkhead end, relief to tip = Air-Way i2 (STEP 2.11 - 0.86 = 1.25 = i2), JIC thread run from the relief to the land; K1 read as the collar thickness (ASSUMPTION: the STEP collar is 0.875 x 0.125 followed by a 0.125 round shank at the thread dia, not modelled); -LN configs ship with a locknut (separate part, not modelled); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells 2701-LN-02-02-FG; copied from 2701-02-02-FG (A10: -LN modelled as the plain part, no locknut)</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2701-04-04-FG</t>
+          <t>2701-LN-02-02-FG</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2701-05-05-FG</t>
+          <t>2701-04-04-FG</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.06</v>
+        <v>0.97</v>
       </c>
       <c r="C5" t="n">
-        <v>0.281</v>
+        <v>0.22</v>
       </c>
       <c r="D5" t="n">
-        <v>0.25</v>
+        <v>0.21875</v>
       </c>
       <c r="E5" t="n">
         <v>0.075</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2606</v>
+        <v>0.2608</v>
       </c>
       <c r="G5" t="n">
-        <v>0.213</v>
+        <v>0.182</v>
       </c>
       <c r="H5" t="n">
         <v>0.0795</v>
@@ -1304,28 +1309,28 @@
         <v>37</v>
       </c>
       <c r="L5" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="M5" t="n">
-        <v>0.261</v>
+        <v>0.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3125</v>
+        <v>0.28</v>
       </c>
       <c r="O5" t="n">
-        <v>0.094</v>
+        <v>0.09</v>
       </c>
       <c r="P5" t="n">
-        <v>0.25</v>
+        <v>0.21875</v>
       </c>
       <c r="Q5" t="n">
         <v>0.075</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7306</v>
+        <v>0.7308</v>
       </c>
       <c r="S5" t="n">
-        <v>0.213</v>
+        <v>0.182</v>
       </c>
       <c r="T5" t="n">
         <v>0.0795</v>
@@ -1340,25 +1345,25 @@
         <v>37</v>
       </c>
       <c r="X5" t="n">
-        <v>0.234</v>
+        <v>0.17</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.06</v>
+        <v>0.97</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.234</v>
+        <v>0.17</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.5</v>
+        <v>0.4375</v>
       </c>
       <c r="AC5" t="n">
         <v>0.05</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.2606</v>
+        <v>0.2608</v>
       </c>
       <c r="AE5" t="n">
         <v>0.02706</v>
@@ -1370,13 +1375,13 @@
         <v>0.05</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.5</v>
+        <v>0.4375</v>
       </c>
       <c r="AI5" t="n">
         <v>0.05</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.7306</v>
+        <v>0.7308</v>
       </c>
       <c r="AK5" t="n">
         <v>0.02706</v>
@@ -1388,40 +1393,40 @@
         <v>0.05</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.51</v>
+        <v>0.42</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.606</v>
+        <v>0.48</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.281</v>
+        <v>0.22</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.281</v>
+        <v>0.22</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.16174</v>
+        <v>0.12652</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.16174</v>
+        <v>0.12652</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.32397</v>
+        <v>0.25353</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2701-05-05-FG</t>
+          <t>2701-04-04-FG</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>90 deg Bulkhead Elbow, 1/2-20 JIC x 1/2-20 JIC bulkhead</t>
+          <t>90 deg Bulkhead Elbow, 7/16-20 JIC x 7/16-20 JIC bulkhead</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1431,12 +1436,12 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1/2-20 JIC</t>
+          <t>7/16-20 JIC</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1/2-20 JIC bulkhead</t>
+          <t>7/16-20 JIC bulkhead</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -1446,49 +1451,44 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING; 2026-10-02 (batch 15): every dimension cell MEASURED on the part's own Brennan STEP 09_STEP_FILES/BRENNAN_2701-05-05-FG.stp (sha256 4ee83f30e2cd..., received 2026-10-02, tools/_out/step_ingest_20261002/MANIFEST_sha256.txt) with the fix2702 bulkhead reading (tools/_out/batch15_20261002/work/FG-STEP/scripts/meas_lib.py bh_leg = tools/_out/fix2702_20261002/scripts/measure_bh.py; validated on the Brennan 2701-08-08-FG STEP of the accepted 2701 master (M3 1.36 / M4 2.11 / i2 1.25 / Y 0.75 / thread majors 0.75 exact; O 0.875 and D 0.391 = the row by rounding; K1 0.125 vs Air-Way 0.09 = the known K1 reading) and by the closed loop on the OCP rebuild of this row: work/FG-STEP/measure/closedloop.txt): M3 1.060 (crossing to the leg-1 JIC tip), M4 1.720 (crossing to the bulkhead tip), Y 0.562 (hex flats; corners 0.3245 = Y/sqrt 3), O 0.625 (bulkhead collar dia), K1 0.094 (collar thickness = the gen_tee reading of K1), i2 1.020 (relief start to tip = the gen_tee reading of i2; the 0.094 long dia 0.494 shank between collar and relief is not modelled, as on every bulkhead row), D1 / D2 0.234 (bores); THDMAJ_B1 / B2 0.5: 1/2-20 = the -05 JIC dash of the part number (STEP thread majors 0.5 on both legs) [standing user decision: a forged -FG part may be built from its own Brennan STEP; one manufacturer -&gt; ASSUMED]. The Brennan TFA catalog p27 (table TFA-p027-t02, page-verified; tools/_out/brennan_catalog_20261001/catalog_verified.json) prints M 1.06, L 1.72, Y FLATS 0.562, B1 / B2 DRILL 0.234 and B1 / B2 1/2-20 = the STEP (same manufacturer, not an independent source; it does not print i2 / K1 / O). The OMi dimension file gives no value for this SKU (07_RAW_EXTRACTS/omi_dimensions/WebsitePartsInfo2026.xlsx Items row 963: part number and description only); Air-Way prints no -05 row. Where the MODEL text below says Air-Way hex / i2 / dia O, this row uses these STEP values | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; bulkhead leg (Brennan 2701-08-08-FG STEP): hex arm -&gt; round collar of Air-Way dia O (flush with the hex flats where Air-Way prints O = the flats, e.g. 2701 -06/-10/-12; the revolved core under the hex arm is drawn 0.02 inside the flats and is hidden by the hex) -&gt; JIC bulkhead end, relief to tip = Air-Way i2 (STEP 2.11 - 0.86 = 1.25 = i2), JIC thread run from the relief to the land; K1 read as the collar thickness (ASSUMPTION: the STEP collar is 0.875 x 0.125 followed by a 0.125 round shank at the thread dia, not modelled); -LN configs ship with a locknut (separate part, not modelled); each leg bore runs from its face to the axis crossing</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-02 (resolved, batch 15): built from its OWN Brennan STEP (09_STEP_FILES/BRENNAN_2701-05-05-FG.stp; one manufacturer -&gt; ASSUMED; the Brennan catalog p27 prints the same legs / hex / drills but is the same source, and prints no i2 / K1 / O); Air-Way has no row for this size. FLAG for the SolidWorks dry run: the bulkhead collar (radius 0.3125) lies between the hex flats (0.2810) and corners (0.3245) - the first 2701 row where the collar crosses the hex outline; that crossing rebuilds on 2702-10/-12/-20, 2703-12 and 2704-10/-12/-16 but HEX2_BODY / HEX3_BODY did not rebuild at 2702 / 2703 -16 (fix2702_20261002); 2701 has no bh_short entry, so the arm ends on the collar face (HEXL@HEX2_BODY 0.606) - check HEX2_BODY on this row</t>
+          <t>Air-Way s123 only (double-pass 33 rows); pass1 stated ROWS=34, both passes enumerate 33; Series sheet n=34 -&gt; 33 accepted | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; bulkhead leg (Brennan 2701-08-08-FG STEP): hex arm -&gt; round collar of Air-Way dia O (flush with the hex flats where Air-Way prints O = the flats, e.g. 2701 -06/-10/-12; the revolved core under the hex arm is drawn 0.02 inside the flats and is hidden by the hex) -&gt; JIC bulkhead end, relief to tip = Air-Way i2 (STEP 2.11 - 0.86 = 1.25 = i2), JIC thread run from the relief to the land; K1 read as the collar thickness (ASSUMPTION: the STEP collar is 0.875 x 0.125 followed by a 0.125 round shank at the thread dia, not modelled); -LN configs ship with a locknut (separate part, not modelled); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2701-05-05-FG</t>
+          <t>2701-04-04-FG</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2701-06-06-FG</t>
+          <t>2701-04-04-FG-LN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.09</v>
+        <v>0.97</v>
       </c>
       <c r="C6" t="n">
-        <v>0.28125</v>
+        <v>0.22</v>
       </c>
       <c r="D6" t="n">
-        <v>0.28125</v>
+        <v>0.21875</v>
       </c>
       <c r="E6" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2515</v>
+        <v>0.2608</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2405</v>
+        <v>0.182</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0898</v>
+        <v>0.0795</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1082</v>
+        <v>0.1135</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
@@ -1497,10 +1497,10 @@
         <v>37</v>
       </c>
       <c r="L6" t="n">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="M6" t="n">
-        <v>0.26125</v>
+        <v>0.2</v>
       </c>
       <c r="N6" t="n">
         <v>0.28</v>
@@ -1509,22 +1509,22 @@
         <v>0.09</v>
       </c>
       <c r="P6" t="n">
-        <v>0.28125</v>
+        <v>0.21875</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7855</v>
+        <v>0.7308</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2405</v>
+        <v>0.182</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0898</v>
+        <v>0.0795</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1082</v>
+        <v>0.1135</v>
       </c>
       <c r="V6" t="n">
         <v>60</v>
@@ -1533,88 +1533,88 @@
         <v>37</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3</v>
+        <v>0.17</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.09</v>
+        <v>0.97</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.3</v>
+        <v>0.17</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.2515</v>
+        <v>0.2608</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.7855</v>
+        <v>0.7308</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.5625</v>
+        <v>0.44</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.534</v>
+        <v>0.42</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.5625</v>
+        <v>0.44</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.63</v>
+        <v>0.48</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.28125</v>
+        <v>0.22</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.28125</v>
+        <v>0.22</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.16188</v>
+        <v>0.12652</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.16188</v>
+        <v>0.12652</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.32426</v>
+        <v>0.25353</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2701-06-06-FG</t>
+          <t>2701-04-04-FG-LN</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>90 deg Bulkhead Elbow, 9/16-18 JIC x 9/16-18 JIC bulkhead</t>
+          <t>90 deg Bulkhead Elbow, 7/16-20 JIC x 7/16-20 JIC bulkhead</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1624,12 +1624,12 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>9/16-18 JIC</t>
+          <t>7/16-20 JIC</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>9/16-18 JIC bulkhead</t>
+          <t>7/16-20 JIC bulkhead</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -1644,44 +1644,44 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>hex A/F raised from Air-Way 0.56 to 0.5625 (JIC thread major; 2603HX rule)</t>
+          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | no Brennan catalog row</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2701-06-06-FG</t>
+          <t>2701-LN-04-04-FG</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2701-06-06-FG-LN</t>
+          <t>2701-05-05-FG</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="C7" t="n">
-        <v>0.28125</v>
+        <v>0.281</v>
       </c>
       <c r="D7" t="n">
-        <v>0.28125</v>
+        <v>0.25</v>
       </c>
       <c r="E7" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2515</v>
+        <v>0.2606</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2405</v>
+        <v>0.213</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0898</v>
+        <v>0.0795</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1082</v>
+        <v>0.1135</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
@@ -1690,34 +1690,34 @@
         <v>37</v>
       </c>
       <c r="L7" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="M7" t="n">
-        <v>0.26125</v>
+        <v>0.261</v>
       </c>
       <c r="N7" t="n">
-        <v>0.28</v>
+        <v>0.3125</v>
       </c>
       <c r="O7" t="n">
-        <v>0.09</v>
+        <v>0.094</v>
       </c>
       <c r="P7" t="n">
-        <v>0.28125</v>
+        <v>0.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7855</v>
+        <v>0.7306</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2405</v>
+        <v>0.213</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0898</v>
+        <v>0.0795</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1082</v>
+        <v>0.1135</v>
       </c>
       <c r="V7" t="n">
         <v>60</v>
@@ -1726,88 +1726,88 @@
         <v>37</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3</v>
+        <v>0.234</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.3</v>
+        <v>0.234</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.5625</v>
+        <v>0.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.2515</v>
+        <v>0.2606</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.5625</v>
+        <v>0.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.7855</v>
+        <v>0.7306</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.5625</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.534</v>
+        <v>0.51</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.5625</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.63</v>
+        <v>0.606</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.28125</v>
+        <v>0.281</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.28125</v>
+        <v>0.281</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.16188</v>
+        <v>0.16174</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.16188</v>
+        <v>0.16174</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.32426</v>
+        <v>0.32397</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2701-06-06-FG-LN</t>
+          <t>2701-05-05-FG</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>90 deg Bulkhead Elbow, 9/16-18 JIC x 9/16-18 JIC bulkhead</t>
+          <t>90 deg Bulkhead Elbow, 1/2-20 JIC x 1/2-20 JIC bulkhead</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>9/16-18 JIC</t>
+          <t>1/2-20 JIC</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>9/16-18 JIC bulkhead</t>
+          <t>1/2-20 JIC bulkhead</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -1832,49 +1832,49 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>Air-Way s123 only (double-pass 33 rows); pass1 stated ROWS=34, both passes enumerate 33; Series sheet n=34 -&gt; 33 accepted | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; bulkhead leg (Brennan 2701-08-08-FG STEP): hex arm -&gt; round collar of Air-Way dia O (flush with the hex flats where Air-Way prints O = the flats, e.g. 2701 -06/-10/-12; the revolved core under the hex arm is drawn 0.02 inside the flats and is hidden by the hex) -&gt; JIC bulkhead end, relief to tip = Air-Way i2 (STEP 2.11 - 0.86 = 1.25 = i2), JIC thread run from the relief to the land; K1 read as the collar thickness (ASSUMPTION: the STEP collar is 0.875 x 0.125 followed by a 0.125 round shank at the thread dia, not modelled); -LN configs ship with a locknut (separate part, not modelled); each leg bore runs from its face to the axis crossing</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING; 2026-10-02 (batch 15): every dimension cell MEASURED on the part's own Brennan STEP 09_STEP_FILES/BRENNAN_2701-05-05-FG.stp (sha256 4ee83f30e2cd..., received 2026-10-02, tools/_out/step_ingest_20261002/MANIFEST_sha256.txt) with the fix2702 bulkhead reading (tools/_out/batch15_20261002/work/FG-STEP/scripts/meas_lib.py bh_leg = tools/_out/fix2702_20261002/scripts/measure_bh.py; validated on the Brennan 2701-08-08-FG STEP of the accepted 2701 master (M3 1.36 / M4 2.11 / i2 1.25 / Y 0.75 / thread majors 0.75 exact; O 0.875 and D 0.391 = the row by rounding; K1 0.125 vs Air-Way 0.09 = the known K1 reading) and by the closed loop on the OCP rebuild of this row: work/FG-STEP/measure/closedloop.txt): M3 1.060 (crossing to the leg-1 JIC tip), M4 1.720 (crossing to the bulkhead tip), Y 0.562 (hex flats; corners 0.3245 = Y/sqrt 3), O 0.625 (bulkhead collar dia), K1 0.094 (collar thickness = the gen_tee reading of K1), i2 1.020 (relief start to tip = the gen_tee reading of i2; the 0.094 long dia 0.494 shank between collar and relief is not modelled, as on every bulkhead row), D1 / D2 0.234 (bores); THDMAJ_B1 / B2 0.5: 1/2-20 = the -05 JIC dash of the part number (STEP thread majors 0.5 on both legs) [standing user decision: a forged -FG part may be built from its own Brennan STEP; one manufacturer -&gt; ASSUMED]. The Brennan TFA catalog p27 (table TFA-p027-t02, page-verified; tools/_out/brennan_catalog_20261001/catalog_verified.json) prints M 1.06, L 1.72, Y FLATS 0.562, B1 / B2 DRILL 0.234 and B1 / B2 1/2-20 = the STEP (same manufacturer, not an independent source; it does not print i2 / K1 / O). The OMi dimension file gives no value for this SKU (07_RAW_EXTRACTS/omi_dimensions/WebsitePartsInfo2026.xlsx Items row 963: part number and description only); Air-Way prints no -05 row. Where the MODEL text below says Air-Way hex / i2 / dia O, this row uses these STEP values | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; bulkhead leg (Brennan 2701-08-08-FG STEP): hex arm -&gt; round collar of Air-Way dia O (flush with the hex flats where Air-Way prints O = the flats, e.g. 2701 -06/-10/-12; the revolved core under the hex arm is drawn 0.02 inside the flats and is hidden by the hex) -&gt; JIC bulkhead end, relief to tip = Air-Way i2 (STEP 2.11 - 0.86 = 1.25 = i2), JIC thread run from the relief to the land; K1 read as the collar thickness (ASSUMPTION: the STEP collar is 0.875 x 0.125 followed by a 0.125 round shank at the thread dia, not modelled); -LN configs ship with a locknut (separate part, not modelled); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>hex A/F raised from Air-Way 0.56 to 0.5625 (JIC thread major; 2603HX rule)</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-02 (resolved, batch 15): built from its OWN Brennan STEP (09_STEP_FILES/BRENNAN_2701-05-05-FG.stp; one manufacturer -&gt; ASSUMED; the Brennan catalog p27 prints the same legs / hex / drills but is the same source, and prints no i2 / K1 / O); Air-Way has no row for this size. FLAG for the SolidWorks dry run: the bulkhead collar (radius 0.3125) lies between the hex flats (0.2810) and corners (0.3245) - the first 2701 row where the collar crosses the hex outline; that crossing rebuilds on 2702-10/-12/-20, 2703-12 and 2704-10/-12/-16 but HEX2_BODY / HEX3_BODY did not rebuild at 2702 / 2703 -16 (fix2702_20261002); 2701 has no bh_short entry, so the arm ends on the collar face (HEXL@HEX2_BODY 0.606) - check HEX2_BODY on this row</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>2701-LN-06-06-FG</t>
+          <t>2701-05-05-FG</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2701-08-08-FG-LN</t>
+          <t>2701-05-05-FG-LN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.36</v>
+        <v>1.06</v>
       </c>
       <c r="C8" t="n">
-        <v>0.375</v>
+        <v>0.281</v>
       </c>
       <c r="D8" t="n">
-        <v>0.375</v>
+        <v>0.25</v>
       </c>
       <c r="E8" t="n">
-        <v>0.094</v>
+        <v>0.075</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2837</v>
+        <v>0.2606</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3295</v>
+        <v>0.213</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0984</v>
+        <v>0.0795</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1546</v>
+        <v>0.1135</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
@@ -1883,34 +1883,34 @@
         <v>37</v>
       </c>
       <c r="L8" t="n">
-        <v>2.11</v>
+        <v>1.72</v>
       </c>
       <c r="M8" t="n">
-        <v>0.355</v>
+        <v>0.261</v>
       </c>
       <c r="N8" t="n">
-        <v>0.44</v>
+        <v>0.3125</v>
       </c>
       <c r="O8" t="n">
-        <v>0.09</v>
+        <v>0.094</v>
       </c>
       <c r="P8" t="n">
-        <v>0.375</v>
+        <v>0.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.094</v>
+        <v>0.075</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8767</v>
+        <v>0.7306</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3295</v>
+        <v>0.213</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0984</v>
+        <v>0.0795</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1546</v>
+        <v>0.1135</v>
       </c>
       <c r="V8" t="n">
         <v>60</v>
@@ -1919,88 +1919,88 @@
         <v>37</v>
       </c>
       <c r="X8" t="n">
-        <v>0.39</v>
+        <v>0.234</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>1.06</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.39</v>
+        <v>0.234</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.11</v>
+        <v>1.72</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0625</v>
+        <v>0.05</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.2837</v>
+        <v>0.2606</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.03383</v>
+        <v>0.02706</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.01562</v>
+        <v>0.0125</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0625</v>
+        <v>0.05</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0625</v>
+        <v>0.05</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.8767</v>
+        <v>0.7306</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.03383</v>
+        <v>0.02706</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.01562</v>
+        <v>0.0125</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0625</v>
+        <v>0.05</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.75</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.703</v>
+        <v>0.51</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.75</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.77</v>
+        <v>0.606</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.375</v>
+        <v>0.281</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.375</v>
+        <v>0.281</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.21601</v>
+        <v>0.16174</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.21601</v>
+        <v>0.16174</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.43251</v>
+        <v>0.32397</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2701-08-08-FG-LN</t>
+          <t>2701-05-05-FG-LN</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>90 deg Bulkhead Elbow, 3/4-16 JIC x 3/4-16 JIC bulkhead</t>
+          <t>90 deg Bulkhead Elbow, 1/2-20 JIC x 1/2-20 JIC bulkhead</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -2010,12 +2010,12 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>3/4-16 JIC</t>
+          <t>1/2-20 JIC</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>3/4-16 JIC bulkhead</t>
+          <t>1/2-20 JIC bulkhead</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -2025,44 +2025,49 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>Air-Way s123 only (double-pass 33 rows); pass1 stated ROWS=34, both passes enumerate 33; Series sheet n=34 -&gt; 33 accepted | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; bulkhead leg (Brennan 2701-08-08-FG STEP): hex arm -&gt; round collar of Air-Way dia O (flush with the hex flats where Air-Way prints O = the flats, e.g. 2701 -06/-10/-12; the revolved core under the hex arm is drawn 0.02 inside the flats and is hidden by the hex) -&gt; JIC bulkhead end, relief to tip = Air-Way i2 (STEP 2.11 - 0.86 = 1.25 = i2), JIC thread run from the relief to the land; K1 read as the collar thickness (ASSUMPTION: the STEP collar is 0.875 x 0.125 followed by a 0.125 round shank at the thread dia, not modelled); -LN configs ship with a locknut (separate part, not modelled); each leg bore runs from its face to the axis crossing</t>
+          <t>OMi catalog SKU 2701-LN-05-05-FG dropped by the 2026-09-23 crawl (adapters77 2026-10-16); -LN = the plain 2701-05-05-FG + a locknut (A10 Q-TRANSFER-LN yes 2026-10-18): every size = row 2701-05-05-FG (its own Brennan STEP, batch 15) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; bulkhead leg (Brennan 2701-08-08-FG STEP): hex arm -&gt; round collar of Air-Way dia O (flush with the hex flats where Air-Way prints O = the flats, e.g. 2701 -06/-10/-12; the revolved core under the hex arm is drawn 0.02 inside the flats and is hidden by the hex) -&gt; JIC bulkhead end, relief to tip = Air-Way i2 (STEP 2.11 - 0.86 = 1.25 = i2), JIC thread run from the relief to the land; K1 read as the collar thickness (ASSUMPTION: the STEP collar is 0.875 x 0.125 followed by a 0.125 round shank at the thread dia, not modelled); -LN configs ship with a locknut (separate part, not modelled); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells 2701-LN-05-05-FG; copied from 2701-05-05-FG (A10: -LN modelled as the plain part, no locknut)</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>2701-LN-08-08-FG</t>
+          <t>2701-LN-05-05-FG</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2701-10-10-FG</t>
+          <t>2701-06-06-FG</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.56</v>
+        <v>1.09</v>
       </c>
       <c r="C9" t="n">
-        <v>0.44</v>
+        <v>0.28125</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4375</v>
+        <v>0.28125</v>
       </c>
       <c r="E9" t="n">
-        <v>0.107</v>
+        <v>0.083</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3553</v>
+        <v>0.2515</v>
       </c>
       <c r="G9" t="n">
-        <v>0.386</v>
+        <v>0.2405</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1114</v>
+        <v>0.0898</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1546</v>
+        <v>0.1082</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
@@ -2071,34 +2076,34 @@
         <v>37</v>
       </c>
       <c r="L9" t="n">
-        <v>2.39</v>
+        <v>1.81</v>
       </c>
       <c r="M9" t="n">
-        <v>0.42</v>
+        <v>0.26125</v>
       </c>
       <c r="N9" t="n">
-        <v>0.44</v>
+        <v>0.28</v>
       </c>
       <c r="O9" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4375</v>
+        <v>0.28125</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.107</v>
+        <v>0.083</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9873</v>
+        <v>0.7855</v>
       </c>
       <c r="S9" t="n">
-        <v>0.386</v>
+        <v>0.2405</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1114</v>
+        <v>0.0898</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1546</v>
+        <v>0.1082</v>
       </c>
       <c r="V9" t="n">
         <v>60</v>
@@ -2107,88 +2112,88 @@
         <v>37</v>
       </c>
       <c r="X9" t="n">
-        <v>0.48</v>
+        <v>0.3</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.56</v>
+        <v>1.09</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.48</v>
+        <v>0.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.39</v>
+        <v>1.81</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.875</v>
+        <v>0.5625</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.3553</v>
+        <v>0.2515</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.03866</v>
+        <v>0.03007</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.01786</v>
+        <v>0.01389</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.875</v>
+        <v>0.5625</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.9873</v>
+        <v>0.7855</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.03866</v>
+        <v>0.03007</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.01786</v>
+        <v>0.01389</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.88</v>
+        <v>0.5625</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.802</v>
+        <v>0.534</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.88</v>
+        <v>0.5625</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.87</v>
+        <v>0.63</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.44</v>
+        <v>0.28125</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.44</v>
+        <v>0.28125</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.25353</v>
+        <v>0.16188</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.25353</v>
+        <v>0.16188</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.50757</v>
+        <v>0.32426</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2701-10-10-FG</t>
+          <t>2701-06-06-FG</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>90 deg Bulkhead Elbow, 7/8-14 JIC x 7/8-14 JIC bulkhead</t>
+          <t>90 deg Bulkhead Elbow, 9/16-18 JIC x 9/16-18 JIC bulkhead</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -2198,12 +2203,12 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>7/8-14 JIC</t>
+          <t>9/16-18 JIC</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>7/8-14 JIC bulkhead</t>
+          <t>9/16-18 JIC bulkhead</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -2216,41 +2221,46 @@
           <t>Air-Way s123 only (double-pass 33 rows); pass1 stated ROWS=34, both passes enumerate 33; Series sheet n=34 -&gt; 33 accepted | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; bulkhead leg (Brennan 2701-08-08-FG STEP): hex arm -&gt; round collar of Air-Way dia O (flush with the hex flats where Air-Way prints O = the flats, e.g. 2701 -06/-10/-12; the revolved core under the hex arm is drawn 0.02 inside the flats and is hidden by the hex) -&gt; JIC bulkhead end, relief to tip = Air-Way i2 (STEP 2.11 - 0.86 = 1.25 = i2), JIC thread run from the relief to the land; K1 read as the collar thickness (ASSUMPTION: the STEP collar is 0.875 x 0.125 followed by a 0.125 round shank at the thread dia, not modelled); -LN configs ship with a locknut (separate part, not modelled); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>hex A/F raised from Air-Way 0.56 to 0.5625 (JIC thread major; 2603HX rule)</t>
+        </is>
+      </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>2701-10-10-FG</t>
+          <t>2701-06-06-FG</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2701-10-10-FG-LN</t>
+          <t>2701-06-06-FG-LN</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.56</v>
+        <v>1.09</v>
       </c>
       <c r="C10" t="n">
-        <v>0.44</v>
+        <v>0.28125</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4375</v>
+        <v>0.28125</v>
       </c>
       <c r="E10" t="n">
-        <v>0.107</v>
+        <v>0.083</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3553</v>
+        <v>0.2515</v>
       </c>
       <c r="G10" t="n">
-        <v>0.386</v>
+        <v>0.2405</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1114</v>
+        <v>0.0898</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1546</v>
+        <v>0.1082</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
@@ -2259,34 +2269,34 @@
         <v>37</v>
       </c>
       <c r="L10" t="n">
-        <v>2.39</v>
+        <v>1.81</v>
       </c>
       <c r="M10" t="n">
-        <v>0.42</v>
+        <v>0.26125</v>
       </c>
       <c r="N10" t="n">
-        <v>0.44</v>
+        <v>0.28</v>
       </c>
       <c r="O10" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4375</v>
+        <v>0.28125</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.107</v>
+        <v>0.083</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9873</v>
+        <v>0.7855</v>
       </c>
       <c r="S10" t="n">
-        <v>0.386</v>
+        <v>0.2405</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1114</v>
+        <v>0.0898</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1546</v>
+        <v>0.1082</v>
       </c>
       <c r="V10" t="n">
         <v>60</v>
@@ -2295,88 +2305,88 @@
         <v>37</v>
       </c>
       <c r="X10" t="n">
-        <v>0.48</v>
+        <v>0.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.56</v>
+        <v>1.09</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.48</v>
+        <v>0.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.39</v>
+        <v>1.81</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.875</v>
+        <v>0.5625</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.3553</v>
+        <v>0.2515</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.03866</v>
+        <v>0.03007</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.01786</v>
+        <v>0.01389</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.875</v>
+        <v>0.5625</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.9873</v>
+        <v>0.7855</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.03866</v>
+        <v>0.03007</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.01786</v>
+        <v>0.01389</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.88</v>
+        <v>0.5625</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.802</v>
+        <v>0.534</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.88</v>
+        <v>0.5625</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.87</v>
+        <v>0.63</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.44</v>
+        <v>0.28125</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.44</v>
+        <v>0.28125</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.25353</v>
+        <v>0.16188</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.25353</v>
+        <v>0.16188</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.50757</v>
+        <v>0.32426</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2701-10-10-FG-LN</t>
+          <t>2701-06-06-FG-LN</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>90 deg Bulkhead Elbow, 7/8-14 JIC x 7/8-14 JIC bulkhead</t>
+          <t>90 deg Bulkhead Elbow, 9/16-18 JIC x 9/16-18 JIC bulkhead</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -2386,12 +2396,12 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>7/8-14 JIC</t>
+          <t>9/16-18 JIC</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>7/8-14 JIC bulkhead</t>
+          <t>9/16-18 JIC bulkhead</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -2404,41 +2414,46 @@
           <t>Air-Way s123 only (double-pass 33 rows); pass1 stated ROWS=34, both passes enumerate 33; Series sheet n=34 -&gt; 33 accepted | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; bulkhead leg (Brennan 2701-08-08-FG STEP): hex arm -&gt; round collar of Air-Way dia O (flush with the hex flats where Air-Way prints O = the flats, e.g. 2701 -06/-10/-12; the revolved core under the hex arm is drawn 0.02 inside the flats and is hidden by the hex) -&gt; JIC bulkhead end, relief to tip = Air-Way i2 (STEP 2.11 - 0.86 = 1.25 = i2), JIC thread run from the relief to the land; K1 read as the collar thickness (ASSUMPTION: the STEP collar is 0.875 x 0.125 followed by a 0.125 round shank at the thread dia, not modelled); -LN configs ship with a locknut (separate part, not modelled); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>hex A/F raised from Air-Way 0.56 to 0.5625 (JIC thread major; 2603HX rule)</t>
+        </is>
+      </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>2701-LN-10-10-FG</t>
+          <t>2701-LN-06-06-FG</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2701-12-12-FG</t>
+          <t>2701-08-08-FG-LN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.78</v>
+        <v>1.36</v>
       </c>
       <c r="C11" t="n">
-        <v>0.53125</v>
+        <v>0.375</v>
       </c>
       <c r="D11" t="n">
-        <v>0.53125</v>
+        <v>0.375</v>
       </c>
       <c r="E11" t="n">
-        <v>0.125</v>
+        <v>0.094</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3895</v>
+        <v>0.2837</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4715</v>
+        <v>0.3295</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1299</v>
+        <v>0.0984</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
@@ -2447,34 +2462,34 @@
         <v>37</v>
       </c>
       <c r="L11" t="n">
-        <v>2.67</v>
+        <v>2.11</v>
       </c>
       <c r="M11" t="n">
-        <v>0.51125</v>
+        <v>0.355</v>
       </c>
       <c r="N11" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="O11" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="P11" t="n">
-        <v>0.53125</v>
+        <v>0.375</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.125</v>
+        <v>0.094</v>
       </c>
       <c r="R11" t="n">
-        <v>1.0855</v>
+        <v>0.8767</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4715</v>
+        <v>0.3295</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1299</v>
+        <v>0.0984</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="V11" t="n">
         <v>60</v>
@@ -2483,88 +2498,88 @@
         <v>37</v>
       </c>
       <c r="X11" t="n">
-        <v>0.61</v>
+        <v>0.39</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.78</v>
+        <v>1.36</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.61</v>
+        <v>0.39</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.67</v>
+        <v>2.11</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.0625</v>
+        <v>0.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.3895</v>
+        <v>0.2837</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.04511</v>
+        <v>0.03383</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.02083</v>
+        <v>0.01562</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.0625</v>
+        <v>0.75</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.0855</v>
+        <v>0.8767</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.04511</v>
+        <v>0.03383</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.02083</v>
+        <v>0.01562</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.0625</v>
+        <v>0.75</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.916</v>
+        <v>0.703</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.0625</v>
+        <v>0.75</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.98</v>
+        <v>0.77</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.53125</v>
+        <v>0.375</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.53125</v>
+        <v>0.375</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.30622</v>
+        <v>0.21601</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.30622</v>
+        <v>0.21601</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.61293</v>
+        <v>0.43251</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2701-12-12-FG</t>
+          <t>2701-08-08-FG-LN</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>90 deg Bulkhead Elbow, 1 1/16-12 JIC x 1 1/16-12 JIC bulkhead</t>
+          <t>90 deg Bulkhead Elbow, 3/4-16 JIC x 3/4-16 JIC bulkhead</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -2574,12 +2589,12 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>1 1/16-12 JIC</t>
+          <t>3/4-16 JIC</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1 1/16-12 JIC bulkhead</t>
+          <t>3/4-16 JIC bulkhead</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
@@ -2592,46 +2607,41 @@
           <t>Air-Way s123 only (double-pass 33 rows); pass1 stated ROWS=34, both passes enumerate 33; Series sheet n=34 -&gt; 33 accepted | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; bulkhead leg (Brennan 2701-08-08-FG STEP): hex arm -&gt; round collar of Air-Way dia O (flush with the hex flats where Air-Way prints O = the flats, e.g. 2701 -06/-10/-12; the revolved core under the hex arm is drawn 0.02 inside the flats and is hidden by the hex) -&gt; JIC bulkhead end, relief to tip = Air-Way i2 (STEP 2.11 - 0.86 = 1.25 = i2), JIC thread run from the relief to the land; K1 read as the collar thickness (ASSUMPTION: the STEP collar is 0.875 x 0.125 followed by a 0.125 round shank at the thread dia, not modelled); -LN configs ship with a locknut (separate part, not modelled); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>hex A/F raised from Air-Way 1.06 to 1.0625 (JIC thread major; 2603HX rule)</t>
-        </is>
-      </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>2701-12-12-FG</t>
+          <t>2701-LN-08-08-FG</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2701-12-12-FG-LN</t>
+          <t>2701-10-10-FG</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.78</v>
+        <v>1.56</v>
       </c>
       <c r="C12" t="n">
-        <v>0.53125</v>
+        <v>0.44</v>
       </c>
       <c r="D12" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="E12" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3895</v>
+        <v>0.3553</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4715</v>
+        <v>0.386</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1299</v>
+        <v>0.1114</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="J12" t="n">
         <v>60</v>
@@ -2640,34 +2650,34 @@
         <v>37</v>
       </c>
       <c r="L12" t="n">
-        <v>2.67</v>
+        <v>2.39</v>
       </c>
       <c r="M12" t="n">
-        <v>0.51125</v>
+        <v>0.42</v>
       </c>
       <c r="N12" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="O12" t="n">
         <v>0.13</v>
       </c>
       <c r="P12" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="R12" t="n">
-        <v>1.0855</v>
+        <v>0.9873</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4715</v>
+        <v>0.386</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1299</v>
+        <v>0.1114</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="V12" t="n">
         <v>60</v>
@@ -2676,88 +2686,88 @@
         <v>37</v>
       </c>
       <c r="X12" t="n">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.78</v>
+        <v>1.56</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.67</v>
+        <v>2.39</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.3895</v>
+        <v>0.3553</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.0855</v>
+        <v>0.9873</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.0625</v>
+        <v>0.88</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.916</v>
+        <v>0.802</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.0625</v>
+        <v>0.88</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.53125</v>
+        <v>0.44</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.53125</v>
+        <v>0.44</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.30622</v>
+        <v>0.25353</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.30622</v>
+        <v>0.25353</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.61293</v>
+        <v>0.50757</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2701-12-12-FG-LN</t>
+          <t>2701-10-10-FG</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>90 deg Bulkhead Elbow, 1 1/16-12 JIC x 1 1/16-12 JIC bulkhead</t>
+          <t>90 deg Bulkhead Elbow, 7/8-14 JIC x 7/8-14 JIC bulkhead</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2767,12 +2777,12 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>1 1/16-12 JIC</t>
+          <t>7/8-14 JIC</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1 1/16-12 JIC bulkhead</t>
+          <t>7/8-14 JIC bulkhead</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
@@ -2785,46 +2795,41 @@
           <t>Air-Way s123 only (double-pass 33 rows); pass1 stated ROWS=34, both passes enumerate 33; Series sheet n=34 -&gt; 33 accepted | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; bulkhead leg (Brennan 2701-08-08-FG STEP): hex arm -&gt; round collar of Air-Way dia O (flush with the hex flats where Air-Way prints O = the flats, e.g. 2701 -06/-10/-12; the revolved core under the hex arm is drawn 0.02 inside the flats and is hidden by the hex) -&gt; JIC bulkhead end, relief to tip = Air-Way i2 (STEP 2.11 - 0.86 = 1.25 = i2), JIC thread run from the relief to the land; K1 read as the collar thickness (ASSUMPTION: the STEP collar is 0.875 x 0.125 followed by a 0.125 round shank at the thread dia, not modelled); -LN configs ship with a locknut (separate part, not modelled); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>hex A/F raised from Air-Way 1.06 to 1.0625 (JIC thread major; 2603HX rule)</t>
-        </is>
-      </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>2701-LN-12-12-FG</t>
+          <t>2701-10-10-FG</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2701-16-16-FG</t>
+          <t>2701-10-10-FG-LN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.94</v>
+        <v>1.56</v>
       </c>
       <c r="C13" t="n">
-        <v>0.65625</v>
+        <v>0.44</v>
       </c>
       <c r="D13" t="n">
-        <v>0.65625</v>
+        <v>0.4375</v>
       </c>
       <c r="E13" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4365</v>
+        <v>0.3553</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5965</v>
+        <v>0.386</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1292</v>
+        <v>0.1114</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1858</v>
+        <v>0.1546</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
@@ -2833,34 +2838,34 @@
         <v>37</v>
       </c>
       <c r="L13" t="n">
-        <v>2.8</v>
+        <v>2.39</v>
       </c>
       <c r="M13" t="n">
-        <v>0.63625</v>
+        <v>0.42</v>
       </c>
       <c r="N13" t="n">
-        <v>0.65</v>
+        <v>0.44</v>
       </c>
       <c r="O13" t="n">
         <v>0.13</v>
       </c>
       <c r="P13" t="n">
-        <v>0.65625</v>
+        <v>0.4375</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="R13" t="n">
-        <v>1.0855</v>
+        <v>0.9873</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5965</v>
+        <v>0.386</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1292</v>
+        <v>0.1114</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1858</v>
+        <v>0.1546</v>
       </c>
       <c r="V13" t="n">
         <v>60</v>
@@ -2869,88 +2874,88 @@
         <v>37</v>
       </c>
       <c r="X13" t="n">
-        <v>0.84</v>
+        <v>0.48</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.94</v>
+        <v>1.56</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.84</v>
+        <v>0.48</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.8</v>
+        <v>2.39</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.3125</v>
+        <v>0.875</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.4365</v>
+        <v>0.3553</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.3125</v>
+        <v>0.875</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.0855</v>
+        <v>0.9873</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.3125</v>
+        <v>0.88</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.029</v>
+        <v>0.802</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.3125</v>
+        <v>0.88</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.11</v>
+        <v>0.87</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.65625</v>
+        <v>0.44</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.65625</v>
+        <v>0.44</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.37839</v>
+        <v>0.25353</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.37839</v>
+        <v>0.25353</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.75727</v>
+        <v>0.50757</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>2701-16-16-FG</t>
+          <t>2701-10-10-FG-LN</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>90 deg Bulkhead Elbow, 1 5/16-12 JIC x 1 5/16-12 JIC bulkhead</t>
+          <t>90 deg Bulkhead Elbow, 7/8-14 JIC x 7/8-14 JIC bulkhead</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2960,12 +2965,12 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>1 5/16-12 JIC</t>
+          <t>7/8-14 JIC</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>1 5/16-12 JIC bulkhead</t>
+          <t>7/8-14 JIC bulkhead</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
@@ -2978,46 +2983,41 @@
           <t>Air-Way s123 only (double-pass 33 rows); pass1 stated ROWS=34, both passes enumerate 33; Series sheet n=34 -&gt; 33 accepted | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; bulkhead leg (Brennan 2701-08-08-FG STEP): hex arm -&gt; round collar of Air-Way dia O (flush with the hex flats where Air-Way prints O = the flats, e.g. 2701 -06/-10/-12; the revolved core under the hex arm is drawn 0.02 inside the flats and is hidden by the hex) -&gt; JIC bulkhead end, relief to tip = Air-Way i2 (STEP 2.11 - 0.86 = 1.25 = i2), JIC thread run from the relief to the land; K1 read as the collar thickness (ASSUMPTION: the STEP collar is 0.875 x 0.125 followed by a 0.125 round shank at the thread dia, not modelled); -LN configs ship with a locknut (separate part, not modelled); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule)</t>
-        </is>
-      </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>2701-16-16-FG</t>
+          <t>2701-LN-10-10-FG</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2701-16-16-FG-LN</t>
+          <t>2701-12-12-FG</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="C14" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="D14" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="E14" t="n">
         <v>0.125</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5965</v>
+        <v>0.4715</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1292</v>
+        <v>0.1299</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1858</v>
+        <v>0.1851</v>
       </c>
       <c r="J14" t="n">
         <v>60</v>
@@ -3026,19 +3026,19 @@
         <v>37</v>
       </c>
       <c r="L14" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="M14" t="n">
-        <v>0.63625</v>
+        <v>0.51125</v>
       </c>
       <c r="N14" t="n">
-        <v>0.65</v>
+        <v>0.53</v>
       </c>
       <c r="O14" t="n">
         <v>0.13</v>
       </c>
       <c r="P14" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="Q14" t="n">
         <v>0.125</v>
@@ -3047,13 +3047,13 @@
         <v>1.0855</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5965</v>
+        <v>0.4715</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1292</v>
+        <v>0.1299</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1858</v>
+        <v>0.1851</v>
       </c>
       <c r="V14" t="n">
         <v>60</v>
@@ -3062,25 +3062,25 @@
         <v>37</v>
       </c>
       <c r="X14" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="AC14" t="n">
         <v>0.08333</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="AE14" t="n">
         <v>0.04511</v>
@@ -3092,7 +3092,7 @@
         <v>0.08333</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="AI14" t="n">
         <v>0.08333</v>
@@ -3110,40 +3110,40 @@
         <v>0.08333</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.029</v>
+        <v>0.916</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.11</v>
+        <v>0.98</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.37839</v>
+        <v>0.30622</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.37839</v>
+        <v>0.30622</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.75727</v>
+        <v>0.61293</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>2701-16-16-FG-LN</t>
+          <t>2701-12-12-FG</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>90 deg Bulkhead Elbow, 1 5/16-12 JIC x 1 5/16-12 JIC bulkhead</t>
+          <t>90 deg Bulkhead Elbow, 1 1/16-12 JIC x 1 1/16-12 JIC bulkhead</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>1 5/16-12 JIC</t>
+          <t>1 1/16-12 JIC</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>1 5/16-12 JIC bulkhead</t>
+          <t>1 1/16-12 JIC bulkhead</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
@@ -3173,44 +3173,44 @@
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule)</t>
+          <t>hex A/F raised from Air-Way 1.06 to 1.0625 (JIC thread major; 2603HX rule)</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>2701-LN-16-16-FG</t>
+          <t>2701-12-12-FG</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2701-20-20-FG</t>
+          <t>2701-12-12-FG-LN</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.17</v>
+        <v>1.78</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.53125</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8125</v>
+        <v>0.53125</v>
       </c>
       <c r="E15" t="n">
         <v>0.125</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4316</v>
+        <v>0.3895</v>
       </c>
       <c r="G15" t="n">
-        <v>0.753</v>
+        <v>0.4715</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1288</v>
+        <v>0.1299</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2382</v>
+        <v>0.1851</v>
       </c>
       <c r="J15" t="n">
         <v>60</v>
@@ -3219,34 +3219,34 @@
         <v>37</v>
       </c>
       <c r="L15" t="n">
-        <v>3.12</v>
+        <v>2.67</v>
       </c>
       <c r="M15" t="n">
-        <v>0.795</v>
+        <v>0.51125</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="O15" t="n">
         <v>0.13</v>
       </c>
       <c r="P15" t="n">
-        <v>0.8125</v>
+        <v>0.53125</v>
       </c>
       <c r="Q15" t="n">
         <v>0.125</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0836</v>
+        <v>1.0855</v>
       </c>
       <c r="S15" t="n">
-        <v>0.753</v>
+        <v>0.4715</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1288</v>
+        <v>0.1299</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2382</v>
+        <v>0.1851</v>
       </c>
       <c r="V15" t="n">
         <v>60</v>
@@ -3255,25 +3255,25 @@
         <v>37</v>
       </c>
       <c r="X15" t="n">
-        <v>1.08</v>
+        <v>0.61</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.17</v>
+        <v>1.78</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.08</v>
+        <v>0.61</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.12</v>
+        <v>2.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.625</v>
+        <v>1.0625</v>
       </c>
       <c r="AC15" t="n">
         <v>0.08333</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.4316</v>
+        <v>0.3895</v>
       </c>
       <c r="AE15" t="n">
         <v>0.04511</v>
@@ -3285,13 +3285,13 @@
         <v>0.08333</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.625</v>
+        <v>1.0625</v>
       </c>
       <c r="AI15" t="n">
         <v>0.08333</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.0836</v>
+        <v>1.0855</v>
       </c>
       <c r="AK15" t="n">
         <v>0.04511</v>
@@ -3303,40 +3303,40 @@
         <v>0.08333</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.63</v>
+        <v>1.0625</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.212</v>
+        <v>0.916</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.63</v>
+        <v>1.0625</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.38</v>
+        <v>0.98</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.53125</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.53125</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.47004</v>
+        <v>0.30622</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.47004</v>
+        <v>0.30622</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.94058</v>
+        <v>0.61293</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>2701-20-20-FG</t>
+          <t>2701-12-12-FG-LN</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>90 deg Bulkhead Elbow, 1 5/8-12 JIC x 1 5/8-12 JIC bulkhead</t>
+          <t>90 deg Bulkhead Elbow, 1 1/16-12 JIC x 1 1/16-12 JIC bulkhead</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -3346,12 +3346,12 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>1 5/8-12 JIC</t>
+          <t>1 1/16-12 JIC</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>1 5/8-12 JIC bulkhead</t>
+          <t>1 1/16-12 JIC bulkhead</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
@@ -3364,41 +3364,46 @@
           <t>Air-Way s123 only (double-pass 33 rows); pass1 stated ROWS=34, both passes enumerate 33; Series sheet n=34 -&gt; 33 accepted | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; bulkhead leg (Brennan 2701-08-08-FG STEP): hex arm -&gt; round collar of Air-Way dia O (flush with the hex flats where Air-Way prints O = the flats, e.g. 2701 -06/-10/-12; the revolved core under the hex arm is drawn 0.02 inside the flats and is hidden by the hex) -&gt; JIC bulkhead end, relief to tip = Air-Way i2 (STEP 2.11 - 0.86 = 1.25 = i2), JIC thread run from the relief to the land; K1 read as the collar thickness (ASSUMPTION: the STEP collar is 0.875 x 0.125 followed by a 0.125 round shank at the thread dia, not modelled); -LN configs ship with a locknut (separate part, not modelled); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>hex A/F raised from Air-Way 1.06 to 1.0625 (JIC thread major; 2603HX rule)</t>
+        </is>
+      </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>2701-20-20-FG</t>
+          <t>2701-LN-12-12-FG</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2701-20-20-FG-LN</t>
+          <t>2701-16-16-FG</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.17</v>
+        <v>1.94</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="E16" t="n">
         <v>0.125</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4316</v>
+        <v>0.4365</v>
       </c>
       <c r="G16" t="n">
-        <v>0.753</v>
+        <v>0.5965</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1288</v>
+        <v>0.1292</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2382</v>
+        <v>0.1858</v>
       </c>
       <c r="J16" t="n">
         <v>60</v>
@@ -3407,34 +3412,34 @@
         <v>37</v>
       </c>
       <c r="L16" t="n">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
       <c r="M16" t="n">
-        <v>0.795</v>
+        <v>0.63625</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="O16" t="n">
         <v>0.13</v>
       </c>
       <c r="P16" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="Q16" t="n">
         <v>0.125</v>
       </c>
       <c r="R16" t="n">
-        <v>1.0836</v>
+        <v>1.0855</v>
       </c>
       <c r="S16" t="n">
-        <v>0.753</v>
+        <v>0.5965</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1288</v>
+        <v>0.1292</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2382</v>
+        <v>0.1858</v>
       </c>
       <c r="V16" t="n">
         <v>60</v>
@@ -3443,25 +3448,25 @@
         <v>37</v>
       </c>
       <c r="X16" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.17</v>
+        <v>1.94</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="AC16" t="n">
         <v>0.08333</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.4316</v>
+        <v>0.4365</v>
       </c>
       <c r="AE16" t="n">
         <v>0.04511</v>
@@ -3473,13 +3478,13 @@
         <v>0.08333</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="AI16" t="n">
         <v>0.08333</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.0836</v>
+        <v>1.0855</v>
       </c>
       <c r="AK16" t="n">
         <v>0.04511</v>
@@ -3491,68 +3496,642 @@
         <v>0.08333</v>
       </c>
       <c r="AN16" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1.029</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.75727</v>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>2701-16-16-FG</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>90 deg Bulkhead Elbow, 1 5/16-12 JIC x 1 5/16-12 JIC bulkhead</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>2701</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>1 5/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>1 5/16-12 JIC bulkhead</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>Air-Way s123 only (double-pass 33 rows); pass1 stated ROWS=34, both passes enumerate 33; Series sheet n=34 -&gt; 33 accepted | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; bulkhead leg (Brennan 2701-08-08-FG STEP): hex arm -&gt; round collar of Air-Way dia O (flush with the hex flats where Air-Way prints O = the flats, e.g. 2701 -06/-10/-12; the revolved core under the hex arm is drawn 0.02 inside the flats and is hidden by the hex) -&gt; JIC bulkhead end, relief to tip = Air-Way i2 (STEP 2.11 - 0.86 = 1.25 = i2), JIC thread run from the relief to the land; K1 read as the collar thickness (ASSUMPTION: the STEP collar is 0.875 x 0.125 followed by a 0.125 round shank at the thread dia, not modelled); -LN configs ship with a locknut (separate part, not modelled); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule)</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>2701-16-16-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2701-16-16-FG-LN</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="J17" t="n">
+        <v>60</v>
+      </c>
+      <c r="K17" t="n">
+        <v>37</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.63625</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.0855</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="V17" t="n">
+        <v>60</v>
+      </c>
+      <c r="W17" t="n">
+        <v>37</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.0855</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1.029</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0.75727</v>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>2701-16-16-FG-LN</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>90 deg Bulkhead Elbow, 1 5/16-12 JIC x 1 5/16-12 JIC bulkhead</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>2701</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>1 5/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>1 5/16-12 JIC bulkhead</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>Air-Way s123 only (double-pass 33 rows); pass1 stated ROWS=34, both passes enumerate 33; Series sheet n=34 -&gt; 33 accepted | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; bulkhead leg (Brennan 2701-08-08-FG STEP): hex arm -&gt; round collar of Air-Way dia O (flush with the hex flats where Air-Way prints O = the flats, e.g. 2701 -06/-10/-12; the revolved core under the hex arm is drawn 0.02 inside the flats and is hidden by the hex) -&gt; JIC bulkhead end, relief to tip = Air-Way i2 (STEP 2.11 - 0.86 = 1.25 = i2), JIC thread run from the relief to the land; K1 read as the collar thickness (ASSUMPTION: the STEP collar is 0.875 x 0.125 followed by a 0.125 round shank at the thread dia, not modelled); -LN configs ship with a locknut (separate part, not modelled); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule)</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>2701-LN-16-16-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2701-20-20-FG</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.4316</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1288</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.2382</v>
+      </c>
+      <c r="J18" t="n">
+        <v>60</v>
+      </c>
+      <c r="K18" t="n">
+        <v>37</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.0836</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.1288</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.2382</v>
+      </c>
+      <c r="V18" t="n">
+        <v>60</v>
+      </c>
+      <c r="W18" t="n">
+        <v>37</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.4316</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.0836</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AN18" t="n">
         <v>1.63</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="AO18" t="n">
         <v>1.212</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AP18" t="n">
         <v>1.63</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AQ18" t="n">
         <v>1.38</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="AR18" t="n">
         <v>0.8149999999999999</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="AS18" t="n">
         <v>0.8149999999999999</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="AT18" t="n">
         <v>0.47004</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="AU18" t="n">
         <v>0.47004</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="AV18" t="n">
         <v>0.94058</v>
       </c>
-      <c r="AW16" t="inlineStr">
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>2701-20-20-FG</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>90 deg Bulkhead Elbow, 1 5/8-12 JIC x 1 5/8-12 JIC bulkhead</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>2701</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>1 5/8-12 JIC</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>1 5/8-12 JIC bulkhead</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>Air-Way s123 only (double-pass 33 rows); pass1 stated ROWS=34, both passes enumerate 33; Series sheet n=34 -&gt; 33 accepted | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; bulkhead leg (Brennan 2701-08-08-FG STEP): hex arm -&gt; round collar of Air-Way dia O (flush with the hex flats where Air-Way prints O = the flats, e.g. 2701 -06/-10/-12; the revolved core under the hex arm is drawn 0.02 inside the flats and is hidden by the hex) -&gt; JIC bulkhead end, relief to tip = Air-Way i2 (STEP 2.11 - 0.86 = 1.25 = i2), JIC thread run from the relief to the land; K1 read as the collar thickness (ASSUMPTION: the STEP collar is 0.875 x 0.125 followed by a 0.125 round shank at the thread dia, not modelled); -LN configs ship with a locknut (separate part, not modelled); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>2701-20-20-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>2701-20-20-FG-LN</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
+      <c r="B19" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.4316</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.1288</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2382</v>
+      </c>
+      <c r="J19" t="n">
+        <v>60</v>
+      </c>
+      <c r="K19" t="n">
+        <v>37</v>
+      </c>
+      <c r="L19" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.0836</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.1288</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.2382</v>
+      </c>
+      <c r="V19" t="n">
+        <v>60</v>
+      </c>
+      <c r="W19" t="n">
+        <v>37</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.4316</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.0836</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1.212</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0.47004</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0.47004</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0.94058</v>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>2701-20-20-FG-LN</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
         <is>
           <t>90 deg Bulkhead Elbow, 1 5/8-12 JIC x 1 5/8-12 JIC bulkhead</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr">
+      <c r="AY19" t="inlineStr">
         <is>
           <t>2701</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
+      <c r="AZ19" t="inlineStr">
         <is>
           <t>1 5/8-12 JIC</t>
         </is>
       </c>
-      <c r="BA16" t="inlineStr">
+      <c r="BA19" t="inlineStr">
         <is>
           <t>1 5/8-12 JIC bulkhead</t>
         </is>
       </c>
-      <c r="BB16" t="inlineStr">
+      <c r="BB19" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="BC16" t="inlineStr">
+      <c r="BC19" t="inlineStr">
         <is>
           <t>Air-Way s123 only (double-pass 33 rows); pass1 stated ROWS=34, both passes enumerate 33; Series sheet n=34 -&gt; 33 accepted | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; bulkhead leg (Brennan 2701-08-08-FG STEP): hex arm -&gt; round collar of Air-Way dia O (flush with the hex flats where Air-Way prints O = the flats, e.g. 2701 -06/-10/-12; the revolved core under the hex arm is drawn 0.02 inside the flats and is hidden by the hex) -&gt; JIC bulkhead end, relief to tip = Air-Way i2 (STEP 2.11 - 0.86 = 1.25 = i2), JIC thread run from the relief to the land; K1 read as the collar thickness (ASSUMPTION: the STEP collar is 0.875 x 0.125 followed by a 0.125 round shank at the thread dia, not modelled); -LN configs ship with a locknut (separate part, not modelled); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="BE16" t="inlineStr">
+      <c r="BE19" t="inlineStr">
         <is>
           <t>2701-LN-20-20-FG</t>
         </is>
